--- a/03_Outputs/Cartama/01_Generalidades/distribucion_territorial.xlsx
+++ b/03_Outputs/Cartama/01_Generalidades/distribucion_territorial.xlsx
@@ -8,6 +8,8 @@
   <sheets>
     <sheet name="distribucion_territorial" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="_fig_01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_mapa00_localizacion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="_mapa01_area" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -20,7 +22,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -30,23 +32,56 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -66,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -75,6 +110,12 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,12 +444,12 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,23 +870,23 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>participacion_area_prov_pct</t>
         </is>
@@ -992,6 +1033,443 @@
       </c>
       <c r="C12">
         <v>0.0340277861077358</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ind_mpio</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>subregion</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>provincia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5145</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5282</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5368</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5390</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5467</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5576</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5679</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5792</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5789</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5856</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5861</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SUROESTE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PROVINCIA CARTAMA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Área municipal (km²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5282</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>258.092599</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5789</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>252.239744</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5368</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>205.000676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5679</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>196.169746</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5861</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>139.67431</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5856</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>126.174758</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5792</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>120.479062</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5145</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>92.057782</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5467</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>76.028452</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5576</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>75.43286</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5390</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>54.296311</v>
       </c>
     </row>
   </sheetData>
